--- a/data/labeled/labeled_test_flow_reviews_1.xlsx
+++ b/data/labeled/labeled_test_flow_reviews_1.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SE363 (1)\data\labeled\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DFFF62-C4EB-4367-B296-A5245365B7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -1483,8 +1489,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1547,13 +1553,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1591,7 +1605,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1625,6 +1639,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1659,9 +1674,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1834,11 +1850,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1017"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="107.109375" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="24.109375" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" customWidth="1"/>
+    <col min="7" max="7" width="24.77734375" customWidth="1"/>
+    <col min="8" max="8" width="28.88671875" customWidth="1"/>
+    <col min="9" max="9" width="27.88671875" customWidth="1"/>
+    <col min="10" max="10" width="18.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1870,7 +1898,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1902,7 +1930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1934,7 +1962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1966,7 +1994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1998,7 +2026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -2030,7 +2058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2062,7 +2090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2094,7 +2122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2126,7 +2154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2158,7 +2186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2190,7 +2218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2222,7 +2250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2254,7 +2282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2286,7 +2314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2318,7 +2346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2350,7 +2378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2382,7 +2410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2414,7 +2442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2446,7 +2474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -2478,7 +2506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2510,7 +2538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -2542,7 +2570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -2574,7 +2602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2606,7 +2634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2638,7 +2666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2670,7 +2698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -2702,7 +2730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -2734,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -2766,7 +2794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -2798,7 +2826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -2830,7 +2858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -2862,7 +2890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2894,7 +2922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -2926,7 +2954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -2958,7 +2986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -2990,7 +3018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -3022,7 +3050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -3054,7 +3082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -3086,7 +3114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:10">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -3118,7 +3146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -3150,7 +3178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -3182,7 +3210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -3214,7 +3242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -3246,7 +3274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -3278,7 +3306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:10">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -3310,7 +3338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>15</v>
       </c>
@@ -3342,7 +3370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>16</v>
       </c>
@@ -3374,7 +3402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -3406,7 +3434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -3438,7 +3466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>19</v>
       </c>
@@ -3470,7 +3498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -3502,7 +3530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>21</v>
       </c>
@@ -3534,7 +3562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -3566,7 +3594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -3598,7 +3626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -3630,7 +3658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -3662,7 +3690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>26</v>
       </c>
@@ -3694,7 +3722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>27</v>
       </c>
@@ -3726,7 +3754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>28</v>
       </c>
@@ -3758,7 +3786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -3790,7 +3818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>29</v>
       </c>
@@ -3822,7 +3850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>30</v>
       </c>
@@ -3854,7 +3882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>31</v>
       </c>
@@ -3886,7 +3914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>32</v>
       </c>
@@ -3918,7 +3946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>33</v>
       </c>
@@ -3950,7 +3978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>34</v>
       </c>
@@ -3982,7 +4010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>35</v>
       </c>
@@ -4014,7 +4042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>36</v>
       </c>
@@ -4046,7 +4074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>37</v>
       </c>
@@ -4078,7 +4106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>38</v>
       </c>
@@ -4110,7 +4138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -4142,7 +4170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -4174,7 +4202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>41</v>
       </c>
@@ -4206,7 +4234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>42</v>
       </c>
@@ -4238,7 +4266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>43</v>
       </c>
@@ -4270,7 +4298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>44</v>
       </c>
@@ -4302,7 +4330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>45</v>
       </c>
@@ -4334,7 +4362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>46</v>
       </c>
@@ -4366,7 +4394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>47</v>
       </c>
@@ -4398,7 +4426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>48</v>
       </c>
@@ -4430,7 +4458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>10</v>
       </c>
@@ -4462,7 +4490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -4494,7 +4522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -4526,7 +4554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -4558,7 +4586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -4590,7 +4618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:10">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>15</v>
       </c>
@@ -4622,7 +4650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>16</v>
       </c>
@@ -4654,7 +4682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>17</v>
       </c>
@@ -4686,7 +4714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -4718,7 +4746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>19</v>
       </c>
@@ -4750,7 +4778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -4782,7 +4810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>21</v>
       </c>
@@ -4814,7 +4842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>22</v>
       </c>
@@ -4846,7 +4874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>23</v>
       </c>
@@ -4878,7 +4906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:10">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>24</v>
       </c>
@@ -4910,7 +4938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>25</v>
       </c>
@@ -4942,7 +4970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -4974,7 +5002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>27</v>
       </c>
@@ -5006,7 +5034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>28</v>
       </c>
@@ -5038,7 +5066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>28</v>
       </c>
@@ -5070,7 +5098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>29</v>
       </c>
@@ -5102,7 +5130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -5134,7 +5162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>31</v>
       </c>
@@ -5166,7 +5194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -5198,7 +5226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>33</v>
       </c>
@@ -5230,7 +5258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>34</v>
       </c>
@@ -5262,7 +5290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:10">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>35</v>
       </c>
@@ -5294,7 +5322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>36</v>
       </c>
@@ -5326,7 +5354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>37</v>
       </c>
@@ -5358,7 +5386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>38</v>
       </c>
@@ -5390,7 +5418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>39</v>
       </c>
@@ -5422,7 +5450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -5454,7 +5482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>41</v>
       </c>
@@ -5486,7 +5514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>42</v>
       </c>
@@ -5518,7 +5546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:10">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>43</v>
       </c>
@@ -5550,7 +5578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>44</v>
       </c>
@@ -5582,7 +5610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>45</v>
       </c>
@@ -5614,7 +5642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>46</v>
       </c>
@@ -5646,7 +5674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>47</v>
       </c>
@@ -5678,7 +5706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>48</v>
       </c>
@@ -5710,7 +5738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>49</v>
       </c>
@@ -5742,7 +5770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:10">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>50</v>
       </c>
@@ -5774,7 +5802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>51</v>
       </c>
@@ -5806,7 +5834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>52</v>
       </c>
@@ -5838,7 +5866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>53</v>
       </c>
@@ -5870,7 +5898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>54</v>
       </c>
@@ -5902,7 +5930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>55</v>
       </c>
@@ -5934,7 +5962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>56</v>
       </c>
@@ -5966,7 +5994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>57</v>
       </c>
@@ -5998,7 +6026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>58</v>
       </c>
@@ -6030,7 +6058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>59</v>
       </c>
@@ -6062,7 +6090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>60</v>
       </c>
@@ -6094,7 +6122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>61</v>
       </c>
@@ -6126,7 +6154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>62</v>
       </c>
@@ -6158,7 +6186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>63</v>
       </c>
@@ -6190,7 +6218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>64</v>
       </c>
@@ -6222,7 +6250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>65</v>
       </c>
@@ -6254,7 +6282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>66</v>
       </c>
@@ -6286,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>67</v>
       </c>
@@ -6318,7 +6346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>68</v>
       </c>
@@ -6350,7 +6378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>69</v>
       </c>
@@ -6382,7 +6410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>70</v>
       </c>
@@ -6414,7 +6442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>71</v>
       </c>
@@ -6446,7 +6474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>72</v>
       </c>
@@ -6478,7 +6506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>73</v>
       </c>
@@ -6510,7 +6538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:10">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>74</v>
       </c>
@@ -6542,7 +6570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>75</v>
       </c>
@@ -6574,7 +6602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>76</v>
       </c>
@@ -6606,7 +6634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>77</v>
       </c>
@@ -6638,7 +6666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:10">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>78</v>
       </c>
@@ -6670,7 +6698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>79</v>
       </c>
@@ -6702,7 +6730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>80</v>
       </c>
@@ -6734,7 +6762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>81</v>
       </c>
@@ -6766,7 +6794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>82</v>
       </c>
@@ -6798,7 +6826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>83</v>
       </c>
@@ -6830,7 +6858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>84</v>
       </c>
@@ -6862,7 +6890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>85</v>
       </c>
@@ -6894,7 +6922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>86</v>
       </c>
@@ -6926,7 +6954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>87</v>
       </c>
@@ -6958,7 +6986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>88</v>
       </c>
@@ -6990,7 +7018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:10">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>89</v>
       </c>
@@ -7022,7 +7050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>90</v>
       </c>
@@ -7054,7 +7082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>91</v>
       </c>
@@ -7086,7 +7114,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>92</v>
       </c>
@@ -7118,7 +7146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>93</v>
       </c>
@@ -7150,7 +7178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>94</v>
       </c>
@@ -7182,7 +7210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:10">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>95</v>
       </c>
@@ -7214,7 +7242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>96</v>
       </c>
@@ -7246,7 +7274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>97</v>
       </c>
@@ -7278,7 +7306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>98</v>
       </c>
@@ -7310,7 +7338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:10">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>49</v>
       </c>
@@ -7342,7 +7370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>50</v>
       </c>
@@ -7374,7 +7402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>51</v>
       </c>
@@ -7406,7 +7434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:10">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>52</v>
       </c>
@@ -7438,7 +7466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>53</v>
       </c>
@@ -7470,7 +7498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>54</v>
       </c>
@@ -7502,7 +7530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>55</v>
       </c>
@@ -7534,7 +7562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>56</v>
       </c>
@@ -7566,7 +7594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>57</v>
       </c>
@@ -7598,7 +7626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>58</v>
       </c>
@@ -7630,7 +7658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>59</v>
       </c>
@@ -7662,7 +7690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>60</v>
       </c>
@@ -7694,7 +7722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>61</v>
       </c>
@@ -7726,7 +7754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>62</v>
       </c>
@@ -7758,7 +7786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>63</v>
       </c>
@@ -7790,7 +7818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>64</v>
       </c>
@@ -7822,7 +7850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>65</v>
       </c>
@@ -7854,7 +7882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>66</v>
       </c>
@@ -7886,7 +7914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>67</v>
       </c>
@@ -7918,7 +7946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>68</v>
       </c>
@@ -7950,7 +7978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>69</v>
       </c>
@@ -7982,7 +8010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>70</v>
       </c>
@@ -8014,7 +8042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>71</v>
       </c>
@@ -8046,7 +8074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:10">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>72</v>
       </c>
@@ -8078,7 +8106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>73</v>
       </c>
@@ -8110,7 +8138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>74</v>
       </c>
@@ -8142,7 +8170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>75</v>
       </c>
@@ -8174,7 +8202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>76</v>
       </c>
@@ -8206,7 +8234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>77</v>
       </c>
@@ -8238,7 +8266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>78</v>
       </c>
@@ -8270,7 +8298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>79</v>
       </c>
@@ -8302,7 +8330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>80</v>
       </c>
@@ -8334,7 +8362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>81</v>
       </c>
@@ -8366,7 +8394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>82</v>
       </c>
@@ -8398,7 +8426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>83</v>
       </c>
@@ -8430,7 +8458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>84</v>
       </c>
@@ -8462,7 +8490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>85</v>
       </c>
@@ -8494,7 +8522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>86</v>
       </c>
@@ -8526,7 +8554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>87</v>
       </c>
@@ -8558,7 +8586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>88</v>
       </c>
@@ -8590,7 +8618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>89</v>
       </c>
@@ -8622,7 +8650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>90</v>
       </c>
@@ -8654,7 +8682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:10">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>91</v>
       </c>
@@ -8686,7 +8714,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>92</v>
       </c>
@@ -8718,7 +8746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>93</v>
       </c>
@@ -8750,7 +8778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>94</v>
       </c>
@@ -8782,7 +8810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>95</v>
       </c>
@@ -8814,7 +8842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>96</v>
       </c>
@@ -8846,7 +8874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>97</v>
       </c>
@@ -8878,7 +8906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:10">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>98</v>
       </c>
@@ -8910,7 +8938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>99</v>
       </c>
@@ -8942,7 +8970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>100</v>
       </c>
@@ -8974,7 +9002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>101</v>
       </c>
@@ -9006,7 +9034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>102</v>
       </c>
@@ -9038,7 +9066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>103</v>
       </c>
@@ -9070,7 +9098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>104</v>
       </c>
@@ -9102,7 +9130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>105</v>
       </c>
@@ -9134,7 +9162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>106</v>
       </c>
@@ -9166,7 +9194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>107</v>
       </c>
@@ -9198,7 +9226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>108</v>
       </c>
@@ -9230,7 +9258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>109</v>
       </c>
@@ -9262,7 +9290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>110</v>
       </c>
@@ -9294,7 +9322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>111</v>
       </c>
@@ -9326,7 +9354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>112</v>
       </c>
@@ -9358,7 +9386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>113</v>
       </c>
@@ -9390,7 +9418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>114</v>
       </c>
@@ -9422,7 +9450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:10">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>115</v>
       </c>
@@ -9454,7 +9482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:10">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>116</v>
       </c>
@@ -9486,7 +9514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:10">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>117</v>
       </c>
@@ -9518,7 +9546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:10">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>118</v>
       </c>
@@ -9550,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:10">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>119</v>
       </c>
@@ -9582,7 +9610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:10">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>120</v>
       </c>
@@ -9614,7 +9642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:10">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>121</v>
       </c>
@@ -9646,7 +9674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:10">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>122</v>
       </c>
@@ -9678,7 +9706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:10">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>123</v>
       </c>
@@ -9710,7 +9738,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="247" spans="1:10">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>124</v>
       </c>
@@ -9742,7 +9770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:10">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>125</v>
       </c>
@@ -9774,7 +9802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:10">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>126</v>
       </c>
@@ -9806,7 +9834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:10">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>127</v>
       </c>
@@ -9838,7 +9866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:10">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>128</v>
       </c>
@@ -9870,7 +9898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:10">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>129</v>
       </c>
@@ -9902,7 +9930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:10">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>130</v>
       </c>
@@ -9934,7 +9962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:10">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>131</v>
       </c>
@@ -9966,7 +9994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:10">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>132</v>
       </c>
@@ -9998,7 +10026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:10">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>133</v>
       </c>
@@ -10030,7 +10058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:10">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>134</v>
       </c>
@@ -10062,7 +10090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:10">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>135</v>
       </c>
@@ -10094,7 +10122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:10">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>136</v>
       </c>
@@ -10126,7 +10154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:10">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>137</v>
       </c>
@@ -10158,7 +10186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:10">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>138</v>
       </c>
@@ -10190,7 +10218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:10">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>139</v>
       </c>
@@ -10222,7 +10250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:10">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>140</v>
       </c>
@@ -10254,7 +10282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:10">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>141</v>
       </c>
@@ -10286,7 +10314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:10">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>142</v>
       </c>
@@ -10318,7 +10346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:10">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>143</v>
       </c>
@@ -10350,7 +10378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:10">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>144</v>
       </c>
@@ -10382,7 +10410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:10">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>145</v>
       </c>
@@ -10414,7 +10442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:10">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>146</v>
       </c>
@@ -10446,7 +10474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:10">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>147</v>
       </c>
@@ -10478,7 +10506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:10">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>99</v>
       </c>
@@ -10510,7 +10538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:10">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>100</v>
       </c>
@@ -10542,7 +10570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:10">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>101</v>
       </c>
@@ -10574,7 +10602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:10">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>102</v>
       </c>
@@ -10606,7 +10634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:10">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>103</v>
       </c>
@@ -10638,7 +10666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:10">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>104</v>
       </c>
@@ -10670,7 +10698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:10">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>105</v>
       </c>
@@ -10702,7 +10730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:10">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>106</v>
       </c>
@@ -10734,7 +10762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:10">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>107</v>
       </c>
@@ -10766,7 +10794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:10">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>108</v>
       </c>
@@ -10798,7 +10826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:10">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>109</v>
       </c>
@@ -10830,7 +10858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:10">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>110</v>
       </c>
@@ -10862,7 +10890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:10">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>111</v>
       </c>
@@ -10894,7 +10922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:10">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>112</v>
       </c>
@@ -10926,7 +10954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:10">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>113</v>
       </c>
@@ -10958,7 +10986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:10">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>114</v>
       </c>
@@ -10990,7 +11018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:10">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>115</v>
       </c>
@@ -11022,7 +11050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:10">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>116</v>
       </c>
@@ -11054,7 +11082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:10">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>117</v>
       </c>
@@ -11086,7 +11114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:10">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>118</v>
       </c>
@@ -11118,7 +11146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:10">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>119</v>
       </c>
@@ -11150,7 +11178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:10">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>120</v>
       </c>
@@ -11182,7 +11210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:10">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>121</v>
       </c>
@@ -11214,7 +11242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:10">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>122</v>
       </c>
@@ -11246,7 +11274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:10">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>123</v>
       </c>
@@ -11278,7 +11306,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="296" spans="1:10">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>124</v>
       </c>
@@ -11310,7 +11338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:10">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>125</v>
       </c>
@@ -11342,7 +11370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:10">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>126</v>
       </c>
@@ -11374,7 +11402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:10">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>127</v>
       </c>
@@ -11406,7 +11434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:10">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>128</v>
       </c>
@@ -11438,7 +11466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:10">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>129</v>
       </c>
@@ -11470,7 +11498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:10">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>130</v>
       </c>
@@ -11502,7 +11530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:10">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>131</v>
       </c>
@@ -11534,7 +11562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:10">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>132</v>
       </c>
@@ -11566,7 +11594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:10">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>133</v>
       </c>
@@ -11598,7 +11626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:10">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>134</v>
       </c>
@@ -11630,7 +11658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:10">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>135</v>
       </c>
@@ -11662,7 +11690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:10">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>136</v>
       </c>
@@ -11694,7 +11722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:10">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>137</v>
       </c>
@@ -11726,7 +11754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:10">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>138</v>
       </c>
@@ -11758,7 +11786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:10">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>139</v>
       </c>
@@ -11790,7 +11818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:10">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>140</v>
       </c>
@@ -11822,7 +11850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:10">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>141</v>
       </c>
@@ -11854,7 +11882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:10">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>142</v>
       </c>
@@ -11886,7 +11914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:10">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>143</v>
       </c>
@@ -11918,7 +11946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:10">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>144</v>
       </c>
@@ -11950,7 +11978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:10">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>145</v>
       </c>
@@ -11982,7 +12010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:10">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>146</v>
       </c>
@@ -12014,7 +12042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:10">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>147</v>
       </c>
@@ -12046,7 +12074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:10">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>148</v>
       </c>
@@ -12078,7 +12106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:10">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>149</v>
       </c>
@@ -12110,7 +12138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:10">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>150</v>
       </c>
@@ -12142,7 +12170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:10">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>151</v>
       </c>
@@ -12174,7 +12202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:10">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>152</v>
       </c>
@@ -12206,7 +12234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:10">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>153</v>
       </c>
@@ -12238,7 +12266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:10">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>154</v>
       </c>
@@ -12270,7 +12298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="327" spans="1:10">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>155</v>
       </c>
@@ -12302,7 +12330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:10">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>156</v>
       </c>
@@ -12334,7 +12362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:10">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>157</v>
       </c>
@@ -12366,7 +12394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:10">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>158</v>
       </c>
@@ -12398,7 +12426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="331" spans="1:10">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>159</v>
       </c>
@@ -12430,7 +12458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:10">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>160</v>
       </c>
@@ -12462,7 +12490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:10">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>161</v>
       </c>
@@ -12494,7 +12522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:10">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>162</v>
       </c>
@@ -12526,7 +12554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:10">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>163</v>
       </c>
@@ -12558,7 +12586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:10">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>164</v>
       </c>
@@ -12590,7 +12618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:10">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>165</v>
       </c>
@@ -12622,7 +12650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="338" spans="1:10">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>166</v>
       </c>
@@ -12654,7 +12682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="339" spans="1:10">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>167</v>
       </c>
@@ -12686,7 +12714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="340" spans="1:10">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>168</v>
       </c>
@@ -12718,7 +12746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:10">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>169</v>
       </c>
@@ -12750,7 +12778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="342" spans="1:10">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>170</v>
       </c>
@@ -12782,7 +12810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="1:10">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>171</v>
       </c>
@@ -12814,7 +12842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="344" spans="1:10">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>172</v>
       </c>
@@ -12846,7 +12874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:10">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>173</v>
       </c>
@@ -12878,7 +12906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="346" spans="1:10">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>174</v>
       </c>
@@ -12910,7 +12938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:10">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>175</v>
       </c>
@@ -12942,7 +12970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="348" spans="1:10">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>176</v>
       </c>
@@ -12974,7 +13002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:10">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>177</v>
       </c>
@@ -13006,7 +13034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:10">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>178</v>
       </c>
@@ -13038,7 +13066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="351" spans="1:10">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>179</v>
       </c>
@@ -13070,7 +13098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="352" spans="1:10">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>180</v>
       </c>
@@ -13102,7 +13130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="353" spans="1:10">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>181</v>
       </c>
@@ -13134,7 +13162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="354" spans="1:10">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>182</v>
       </c>
@@ -13166,7 +13194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:10">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>183</v>
       </c>
@@ -13198,7 +13226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:10">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>184</v>
       </c>
@@ -13230,7 +13258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:10">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>185</v>
       </c>
@@ -13262,7 +13290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:10">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>186</v>
       </c>
@@ -13294,7 +13322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="359" spans="1:10">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>187</v>
       </c>
@@ -13326,7 +13354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:10">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>188</v>
       </c>
@@ -13358,7 +13386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="361" spans="1:10">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>189</v>
       </c>
@@ -13390,7 +13418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="362" spans="1:10">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>190</v>
       </c>
@@ -13422,7 +13450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:10">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>191</v>
       </c>
@@ -13454,7 +13482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="364" spans="1:10">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>192</v>
       </c>
@@ -13486,7 +13514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="365" spans="1:10">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>193</v>
       </c>
@@ -13518,7 +13546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:10">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>194</v>
       </c>
@@ -13550,7 +13578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:10">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>195</v>
       </c>
@@ -13582,7 +13610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="1:10">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>196</v>
       </c>
@@ -13614,7 +13642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="369" spans="1:10">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>197</v>
       </c>
@@ -13646,7 +13674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="370" spans="1:10">
+    <row r="370" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>148</v>
       </c>
@@ -13678,7 +13706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:10">
+    <row r="371" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>149</v>
       </c>
@@ -13710,7 +13738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="372" spans="1:10">
+    <row r="372" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>150</v>
       </c>
@@ -13742,7 +13770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="373" spans="1:10">
+    <row r="373" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>151</v>
       </c>
@@ -13774,7 +13802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="374" spans="1:10">
+    <row r="374" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>152</v>
       </c>
@@ -13806,7 +13834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:10">
+    <row r="375" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>153</v>
       </c>
@@ -13838,7 +13866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="376" spans="1:10">
+    <row r="376" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>154</v>
       </c>
@@ -13870,7 +13898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:10">
+    <row r="377" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>155</v>
       </c>
@@ -13902,7 +13930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:10">
+    <row r="378" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>156</v>
       </c>
@@ -13934,7 +13962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="379" spans="1:10">
+    <row r="379" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>157</v>
       </c>
@@ -13966,7 +13994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:10">
+    <row r="380" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>158</v>
       </c>
@@ -13998,7 +14026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="381" spans="1:10">
+    <row r="381" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>159</v>
       </c>
@@ -14030,7 +14058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:10">
+    <row r="382" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>160</v>
       </c>
@@ -14062,7 +14090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="383" spans="1:10">
+    <row r="383" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>161</v>
       </c>
@@ -14094,7 +14122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="384" spans="1:10">
+    <row r="384" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>162</v>
       </c>
@@ -14126,7 +14154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="385" spans="1:10">
+    <row r="385" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>163</v>
       </c>
@@ -14158,7 +14186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:10">
+    <row r="386" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>164</v>
       </c>
@@ -14190,7 +14218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:10">
+    <row r="387" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>165</v>
       </c>
@@ -14222,7 +14250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="388" spans="1:10">
+    <row r="388" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>166</v>
       </c>
@@ -14254,7 +14282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:10">
+    <row r="389" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>167</v>
       </c>
@@ -14286,7 +14314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="390" spans="1:10">
+    <row r="390" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>168</v>
       </c>
@@ -14318,7 +14346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="391" spans="1:10">
+    <row r="391" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>169</v>
       </c>
@@ -14350,7 +14378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:10">
+    <row r="392" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>170</v>
       </c>
@@ -14382,7 +14410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="393" spans="1:10">
+    <row r="393" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>171</v>
       </c>
@@ -14414,7 +14442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="394" spans="1:10">
+    <row r="394" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>172</v>
       </c>
@@ -14446,7 +14474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:10">
+    <row r="395" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>173</v>
       </c>
@@ -14478,7 +14506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:10">
+    <row r="396" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>174</v>
       </c>
@@ -14510,7 +14538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:10">
+    <row r="397" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>175</v>
       </c>
@@ -14542,7 +14570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:10">
+    <row r="398" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>176</v>
       </c>
@@ -14574,7 +14602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="399" spans="1:10">
+    <row r="399" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>177</v>
       </c>
@@ -14606,7 +14634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="400" spans="1:10">
+    <row r="400" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>178</v>
       </c>
@@ -14638,7 +14666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:10">
+    <row r="401" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>179</v>
       </c>
@@ -14670,7 +14698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="402" spans="1:10">
+    <row r="402" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>180</v>
       </c>
@@ -14702,7 +14730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="403" spans="1:10">
+    <row r="403" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>181</v>
       </c>
@@ -14734,7 +14762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:10">
+    <row r="404" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>182</v>
       </c>
@@ -14766,7 +14794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="405" spans="1:10">
+    <row r="405" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>183</v>
       </c>
@@ -14798,7 +14826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="406" spans="1:10">
+    <row r="406" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>184</v>
       </c>
@@ -14830,7 +14858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="407" spans="1:10">
+    <row r="407" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>185</v>
       </c>
@@ -14862,7 +14890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:10">
+    <row r="408" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>186</v>
       </c>
@@ -14894,7 +14922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="409" spans="1:10">
+    <row r="409" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>187</v>
       </c>
@@ -14926,7 +14954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:10">
+    <row r="410" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>188</v>
       </c>
@@ -14958,7 +14986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="411" spans="1:10">
+    <row r="411" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>189</v>
       </c>
@@ -14990,7 +15018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="412" spans="1:10">
+    <row r="412" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>190</v>
       </c>
@@ -15022,7 +15050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:10">
+    <row r="413" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>191</v>
       </c>
@@ -15054,7 +15082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="414" spans="1:10">
+    <row r="414" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>192</v>
       </c>
@@ -15086,7 +15114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="415" spans="1:10">
+    <row r="415" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>193</v>
       </c>
@@ -15118,7 +15146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:10">
+    <row r="416" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>194</v>
       </c>
@@ -15150,7 +15178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="417" spans="1:10">
+    <row r="417" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>195</v>
       </c>
@@ -15182,7 +15210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="418" spans="1:10">
+    <row r="418" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>196</v>
       </c>
@@ -15214,7 +15242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="419" spans="1:10">
+    <row r="419" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>197</v>
       </c>
@@ -15246,7 +15274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:10">
+    <row r="420" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>198</v>
       </c>
@@ -15278,7 +15306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:10">
+    <row r="421" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>199</v>
       </c>
@@ -15310,7 +15338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="422" spans="1:10">
+    <row r="422" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>200</v>
       </c>
@@ -15342,7 +15370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:10">
+    <row r="423" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>201</v>
       </c>
@@ -15374,7 +15402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="424" spans="1:10">
+    <row r="424" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>202</v>
       </c>
@@ -15406,7 +15434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:10">
+    <row r="425" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>203</v>
       </c>
@@ -15438,7 +15466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:10">
+    <row r="426" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>204</v>
       </c>
@@ -15470,7 +15498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="427" spans="1:10">
+    <row r="427" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>205</v>
       </c>
@@ -15502,7 +15530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="428" spans="1:10">
+    <row r="428" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>206</v>
       </c>
@@ -15534,7 +15562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:10">
+    <row r="429" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>207</v>
       </c>
@@ -15566,7 +15594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="430" spans="1:10">
+    <row r="430" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>208</v>
       </c>
@@ -15598,7 +15626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:10">
+    <row r="431" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>209</v>
       </c>
@@ -15630,7 +15658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432" spans="1:10">
+    <row r="432" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>210</v>
       </c>
@@ -15662,7 +15690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:10">
+    <row r="433" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>211</v>
       </c>
@@ -15694,7 +15722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="434" spans="1:10">
+    <row r="434" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>212</v>
       </c>
@@ -15726,7 +15754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="435" spans="1:10">
+    <row r="435" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>213</v>
       </c>
@@ -15758,7 +15786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="436" spans="1:10">
+    <row r="436" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>214</v>
       </c>
@@ -15790,7 +15818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="437" spans="1:10">
+    <row r="437" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>215</v>
       </c>
@@ -15822,7 +15850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:10">
+    <row r="438" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>216</v>
       </c>
@@ -15854,7 +15882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="439" spans="1:10">
+    <row r="439" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>217</v>
       </c>
@@ -15886,7 +15914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="1:10">
+    <row r="440" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>218</v>
       </c>
@@ -15918,7 +15946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="441" spans="1:10">
+    <row r="441" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>219</v>
       </c>
@@ -15950,7 +15978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:10">
+    <row r="442" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>220</v>
       </c>
@@ -15982,7 +16010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="443" spans="1:10">
+    <row r="443" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>221</v>
       </c>
@@ -16014,7 +16042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="444" spans="1:10">
+    <row r="444" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>222</v>
       </c>
@@ -16046,7 +16074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="445" spans="1:10">
+    <row r="445" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>223</v>
       </c>
@@ -16078,7 +16106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="446" spans="1:10">
+    <row r="446" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>224</v>
       </c>
@@ -16110,7 +16138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="447" spans="1:10">
+    <row r="447" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>225</v>
       </c>
@@ -16142,7 +16170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="448" spans="1:10">
+    <row r="448" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>226</v>
       </c>
@@ -16174,7 +16202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="449" spans="1:10">
+    <row r="449" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>227</v>
       </c>
@@ -16206,7 +16234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="450" spans="1:10">
+    <row r="450" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>228</v>
       </c>
@@ -16238,7 +16266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:10">
+    <row r="451" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>229</v>
       </c>
@@ -16270,7 +16298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="452" spans="1:10">
+    <row r="452" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>230</v>
       </c>
@@ -16302,7 +16330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="453" spans="1:10">
+    <row r="453" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>231</v>
       </c>
@@ -16334,7 +16362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="454" spans="1:10">
+    <row r="454" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>232</v>
       </c>
@@ -16366,7 +16394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:10">
+    <row r="455" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>233</v>
       </c>
@@ -16398,7 +16426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="456" spans="1:10">
+    <row r="456" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>234</v>
       </c>
@@ -16430,7 +16458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:10">
+    <row r="457" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>235</v>
       </c>
@@ -16462,7 +16490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="458" spans="1:10">
+    <row r="458" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>236</v>
       </c>
@@ -16494,7 +16522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="459" spans="1:10">
+    <row r="459" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>237</v>
       </c>
@@ -16526,7 +16554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460" spans="1:10">
+    <row r="460" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>238</v>
       </c>
@@ -16558,7 +16586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="461" spans="1:10">
+    <row r="461" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>239</v>
       </c>
@@ -16590,7 +16618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="462" spans="1:10">
+    <row r="462" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>240</v>
       </c>
@@ -16622,7 +16650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="463" spans="1:10">
+    <row r="463" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>233</v>
       </c>
@@ -16654,7 +16682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464" spans="1:10">
+    <row r="464" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>241</v>
       </c>
@@ -16686,7 +16714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465" spans="1:10">
+    <row r="465" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>242</v>
       </c>
@@ -16718,7 +16746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="466" spans="1:10">
+    <row r="466" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>243</v>
       </c>
@@ -16750,7 +16778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="467" spans="1:10">
+    <row r="467" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>244</v>
       </c>
@@ -16782,7 +16810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="468" spans="1:10">
+    <row r="468" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>245</v>
       </c>
@@ -16814,7 +16842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:10">
+    <row r="469" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>246</v>
       </c>
@@ -16846,7 +16874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="470" spans="1:10">
+    <row r="470" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>198</v>
       </c>
@@ -16878,7 +16906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:10">
+    <row r="471" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>199</v>
       </c>
@@ -16910,7 +16938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:10">
+    <row r="472" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>200</v>
       </c>
@@ -16942,7 +16970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="473" spans="1:10">
+    <row r="473" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>201</v>
       </c>
@@ -16974,7 +17002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="474" spans="1:10">
+    <row r="474" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>202</v>
       </c>
@@ -17006,7 +17034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="475" spans="1:10">
+    <row r="475" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>203</v>
       </c>
@@ -17038,7 +17066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:10">
+    <row r="476" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>204</v>
       </c>
@@ -17070,7 +17098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="477" spans="1:10">
+    <row r="477" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>205</v>
       </c>
@@ -17102,7 +17130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:10">
+    <row r="478" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>206</v>
       </c>
@@ -17134,7 +17162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="479" spans="1:10">
+    <row r="479" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>207</v>
       </c>
@@ -17166,7 +17194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="480" spans="1:10">
+    <row r="480" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>208</v>
       </c>
@@ -17198,7 +17226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="481" spans="1:10">
+    <row r="481" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>209</v>
       </c>
@@ -17230,7 +17258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="482" spans="1:10">
+    <row r="482" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>210</v>
       </c>
@@ -17262,7 +17290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:10">
+    <row r="483" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>211</v>
       </c>
@@ -17294,7 +17322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:10">
+    <row r="484" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>212</v>
       </c>
@@ -17326,7 +17354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="485" spans="1:10">
+    <row r="485" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>213</v>
       </c>
@@ -17358,7 +17386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="486" spans="1:10">
+    <row r="486" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>214</v>
       </c>
@@ -17390,7 +17418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:10">
+    <row r="487" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>215</v>
       </c>
@@ -17422,7 +17450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:10">
+    <row r="488" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>216</v>
       </c>
@@ -17454,7 +17482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="489" spans="1:10">
+    <row r="489" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>217</v>
       </c>
@@ -17486,7 +17514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:10">
+    <row r="490" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>218</v>
       </c>
@@ -17518,7 +17546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:10">
+    <row r="491" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>219</v>
       </c>
@@ -17550,7 +17578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:10">
+    <row r="492" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>220</v>
       </c>
@@ -17582,7 +17610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493" spans="1:10">
+    <row r="493" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>221</v>
       </c>
@@ -17614,7 +17642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="494" spans="1:10">
+    <row r="494" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>222</v>
       </c>
@@ -17646,7 +17674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="495" spans="1:10">
+    <row r="495" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>223</v>
       </c>
@@ -17678,7 +17706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:10">
+    <row r="496" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>224</v>
       </c>
@@ -17710,7 +17738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:10">
+    <row r="497" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>225</v>
       </c>
@@ -17742,7 +17770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="498" spans="1:10">
+    <row r="498" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>226</v>
       </c>
@@ -17774,7 +17802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:10">
+    <row r="499" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>227</v>
       </c>
@@ -17806,7 +17834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:10">
+    <row r="500" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>228</v>
       </c>
@@ -17838,7 +17866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:10">
+    <row r="501" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>229</v>
       </c>
@@ -17870,7 +17898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:10">
+    <row r="502" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>230</v>
       </c>
@@ -17902,7 +17930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:10">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>231</v>
       </c>
@@ -17934,7 +17962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="504" spans="1:10">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>232</v>
       </c>
@@ -17966,7 +17994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="505" spans="1:10">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>233</v>
       </c>
@@ -17998,7 +18026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="506" spans="1:10">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>234</v>
       </c>
@@ -18030,7 +18058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="507" spans="1:10">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>235</v>
       </c>
@@ -18062,7 +18090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="508" spans="1:10">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>236</v>
       </c>
@@ -18094,7 +18122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="509" spans="1:10">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>237</v>
       </c>
@@ -18126,7 +18154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:10">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>238</v>
       </c>
@@ -18158,7 +18186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:10">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>239</v>
       </c>
@@ -18190,7 +18218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:10">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>240</v>
       </c>
@@ -18222,7 +18250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="513" spans="1:10">
+    <row r="513" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>233</v>
       </c>
@@ -18254,7 +18282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="514" spans="1:10">
+    <row r="514" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>241</v>
       </c>
@@ -18286,7 +18314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="1:10">
+    <row r="515" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>242</v>
       </c>
@@ -18318,7 +18346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516" spans="1:10">
+    <row r="516" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>243</v>
       </c>
@@ -18350,7 +18378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="517" spans="1:10">
+    <row r="517" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>244</v>
       </c>
@@ -18382,7 +18410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="518" spans="1:10">
+    <row r="518" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>245</v>
       </c>
@@ -18414,7 +18442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:10">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>246</v>
       </c>
@@ -18446,7 +18474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:10">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>247</v>
       </c>
@@ -18478,7 +18506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="521" spans="1:10">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>248</v>
       </c>
@@ -18510,7 +18538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="1:10">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>249</v>
       </c>
@@ -18542,7 +18570,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="523" spans="1:10">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>250</v>
       </c>
@@ -18574,7 +18602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="524" spans="1:10">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>251</v>
       </c>
@@ -18606,7 +18634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:10">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>252</v>
       </c>
@@ -18638,7 +18666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="526" spans="1:10">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>253</v>
       </c>
@@ -18670,7 +18698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="527" spans="1:10">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>254</v>
       </c>
@@ -18702,7 +18730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:10">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>255</v>
       </c>
@@ -18734,7 +18762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:10">
+    <row r="529" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>256</v>
       </c>
@@ -18766,7 +18794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:10">
+    <row r="530" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>257</v>
       </c>
@@ -18798,7 +18826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:10">
+    <row r="531" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>258</v>
       </c>
@@ -18830,7 +18858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:10">
+    <row r="532" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>259</v>
       </c>
@@ -18862,7 +18890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="533" spans="1:10">
+    <row r="533" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>260</v>
       </c>
@@ -18894,7 +18922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="534" spans="1:10">
+    <row r="534" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>261</v>
       </c>
@@ -18926,7 +18954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="535" spans="1:10">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>262</v>
       </c>
@@ -18958,7 +18986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="536" spans="1:10">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>263</v>
       </c>
@@ -18990,7 +19018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:10">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>264</v>
       </c>
@@ -19022,7 +19050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="538" spans="1:10">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>265</v>
       </c>
@@ -19054,7 +19082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:10">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>266</v>
       </c>
@@ -19086,7 +19114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="540" spans="1:10">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>267</v>
       </c>
@@ -19118,7 +19146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="541" spans="1:10">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>268</v>
       </c>
@@ -19150,7 +19178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="542" spans="1:10">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>269</v>
       </c>
@@ -19182,7 +19210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="543" spans="1:10">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>270</v>
       </c>
@@ -19214,7 +19242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="544" spans="1:10">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>271</v>
       </c>
@@ -19246,7 +19274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="545" spans="1:10">
+    <row r="545" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>272</v>
       </c>
@@ -19278,7 +19306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="546" spans="1:10">
+    <row r="546" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>273</v>
       </c>
@@ -19310,7 +19338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="547" spans="1:10">
+    <row r="547" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>274</v>
       </c>
@@ -19342,7 +19370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="548" spans="1:10">
+    <row r="548" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>275</v>
       </c>
@@ -19374,7 +19402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="549" spans="1:10">
+    <row r="549" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>276</v>
       </c>
@@ -19406,7 +19434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="550" spans="1:10">
+    <row r="550" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>277</v>
       </c>
@@ -19438,7 +19466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:10">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>278</v>
       </c>
@@ -19470,7 +19498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="552" spans="1:10">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>279</v>
       </c>
@@ -19502,7 +19530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="553" spans="1:10">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>280</v>
       </c>
@@ -19534,7 +19562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="554" spans="1:10">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>281</v>
       </c>
@@ -19566,7 +19594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:10">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>282</v>
       </c>
@@ -19598,7 +19626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="556" spans="1:10">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>283</v>
       </c>
@@ -19630,7 +19658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="557" spans="1:10">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>277</v>
       </c>
@@ -19662,7 +19690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="558" spans="1:10">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>284</v>
       </c>
@@ -19694,7 +19722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="559" spans="1:10">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>285</v>
       </c>
@@ -19726,7 +19754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="560" spans="1:10">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>286</v>
       </c>
@@ -19758,7 +19786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="561" spans="1:10">
+    <row r="561" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>287</v>
       </c>
@@ -19790,7 +19818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="562" spans="1:10">
+    <row r="562" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>288</v>
       </c>
@@ -19822,7 +19850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="563" spans="1:10">
+    <row r="563" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>289</v>
       </c>
@@ -19854,7 +19882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="564" spans="1:10">
+    <row r="564" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>290</v>
       </c>
@@ -19886,7 +19914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:10">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>291</v>
       </c>
@@ -19918,7 +19946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="566" spans="1:10">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>292</v>
       </c>
@@ -19950,7 +19978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="567" spans="1:10">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>293</v>
       </c>
@@ -19982,7 +20010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="568" spans="1:10">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>294</v>
       </c>
@@ -20014,7 +20042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="569" spans="1:10">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>295</v>
       </c>
@@ -20046,7 +20074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="570" spans="1:10">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>247</v>
       </c>
@@ -20078,7 +20106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="571" spans="1:10">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>248</v>
       </c>
@@ -20110,7 +20138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="572" spans="1:10">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>249</v>
       </c>
@@ -20142,7 +20170,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="573" spans="1:10">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>250</v>
       </c>
@@ -20174,7 +20202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="574" spans="1:10">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>251</v>
       </c>
@@ -20206,7 +20234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="575" spans="1:10">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>252</v>
       </c>
@@ -20238,7 +20266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="576" spans="1:10">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>253</v>
       </c>
@@ -20270,7 +20298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="577" spans="1:10">
+    <row r="577" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>254</v>
       </c>
@@ -20302,7 +20330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="578" spans="1:10">
+    <row r="578" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>255</v>
       </c>
@@ -20334,7 +20362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="1:10">
+    <row r="579" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>256</v>
       </c>
@@ -20366,7 +20394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="580" spans="1:10">
+    <row r="580" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>257</v>
       </c>
@@ -20398,7 +20426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:10">
+    <row r="581" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>258</v>
       </c>
@@ -20430,7 +20458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="582" spans="1:10">
+    <row r="582" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>259</v>
       </c>
@@ -20462,7 +20490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="583" spans="1:10">
+    <row r="583" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>260</v>
       </c>
@@ -20494,7 +20522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="584" spans="1:10">
+    <row r="584" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>261</v>
       </c>
@@ -20526,7 +20554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="585" spans="1:10">
+    <row r="585" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>262</v>
       </c>
@@ -20558,7 +20586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="586" spans="1:10">
+    <row r="586" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>263</v>
       </c>
@@ -20590,7 +20618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="587" spans="1:10">
+    <row r="587" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>264</v>
       </c>
@@ -20622,7 +20650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:10">
+    <row r="588" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>265</v>
       </c>
@@ -20654,7 +20682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="589" spans="1:10">
+    <row r="589" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>266</v>
       </c>
@@ -20686,7 +20714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="590" spans="1:10">
+    <row r="590" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>267</v>
       </c>
@@ -20718,7 +20746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="591" spans="1:10">
+    <row r="591" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>268</v>
       </c>
@@ -20750,7 +20778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="592" spans="1:10">
+    <row r="592" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>269</v>
       </c>
@@ -20782,7 +20810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="593" spans="1:10">
+    <row r="593" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>270</v>
       </c>
@@ -20814,7 +20842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="594" spans="1:10">
+    <row r="594" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>271</v>
       </c>
@@ -20846,7 +20874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="595" spans="1:10">
+    <row r="595" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>272</v>
       </c>
@@ -20878,7 +20906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="596" spans="1:10">
+    <row r="596" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>273</v>
       </c>
@@ -20910,7 +20938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="597" spans="1:10">
+    <row r="597" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>274</v>
       </c>
@@ -20942,7 +20970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:10">
+    <row r="598" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>275</v>
       </c>
@@ -20974,7 +21002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="599" spans="1:10">
+    <row r="599" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>276</v>
       </c>
@@ -21006,7 +21034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:10">
+    <row r="600" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>277</v>
       </c>
@@ -21038,7 +21066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:10">
+    <row r="601" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>278</v>
       </c>
@@ -21070,7 +21098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="602" spans="1:10">
+    <row r="602" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>279</v>
       </c>
@@ -21102,7 +21130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="603" spans="1:10">
+    <row r="603" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>280</v>
       </c>
@@ -21134,7 +21162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="604" spans="1:10">
+    <row r="604" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>281</v>
       </c>
@@ -21166,7 +21194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="605" spans="1:10">
+    <row r="605" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>282</v>
       </c>
@@ -21198,7 +21226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="1:10">
+    <row r="606" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>283</v>
       </c>
@@ -21230,7 +21258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="607" spans="1:10">
+    <row r="607" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>277</v>
       </c>
@@ -21262,7 +21290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="608" spans="1:10">
+    <row r="608" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>284</v>
       </c>
@@ -21294,7 +21322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="609" spans="1:10">
+    <row r="609" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>285</v>
       </c>
@@ -21326,7 +21354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="610" spans="1:10">
+    <row r="610" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>286</v>
       </c>
@@ -21358,7 +21386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="611" spans="1:10">
+    <row r="611" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>287</v>
       </c>
@@ -21390,7 +21418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="612" spans="1:10">
+    <row r="612" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>288</v>
       </c>
@@ -21422,7 +21450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="613" spans="1:10">
+    <row r="613" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>289</v>
       </c>
@@ -21454,7 +21482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="614" spans="1:10">
+    <row r="614" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>290</v>
       </c>
@@ -21486,7 +21514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="615" spans="1:10">
+    <row r="615" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>291</v>
       </c>
@@ -21518,7 +21546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="616" spans="1:10">
+    <row r="616" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>292</v>
       </c>
@@ -21550,7 +21578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="617" spans="1:10">
+    <row r="617" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>293</v>
       </c>
@@ -21582,7 +21610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:10">
+    <row r="618" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>294</v>
       </c>
@@ -21614,7 +21642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="619" spans="1:10">
+    <row r="619" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>295</v>
       </c>
@@ -21646,7 +21674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:10">
+    <row r="620" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>296</v>
       </c>
@@ -21678,7 +21706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="621" spans="1:10">
+    <row r="621" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>297</v>
       </c>
@@ -21710,7 +21738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="622" spans="1:10">
+    <row r="622" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>298</v>
       </c>
@@ -21742,7 +21770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="623" spans="1:10">
+    <row r="623" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>299</v>
       </c>
@@ -21774,7 +21802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="624" spans="1:10">
+    <row r="624" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>300</v>
       </c>
@@ -21806,7 +21834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:10">
+    <row r="625" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>301</v>
       </c>
@@ -21838,7 +21866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:10">
+    <row r="626" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>302</v>
       </c>
@@ -21870,7 +21898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:10">
+    <row r="627" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>303</v>
       </c>
@@ -21902,7 +21930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:10">
+    <row r="628" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>304</v>
       </c>
@@ -21934,7 +21962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="629" spans="1:10">
+    <row r="629" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>305</v>
       </c>
@@ -21966,7 +21994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="630" spans="1:10">
+    <row r="630" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>306</v>
       </c>
@@ -21998,7 +22026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="631" spans="1:10">
+    <row r="631" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>307</v>
       </c>
@@ -22030,7 +22058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="632" spans="1:10">
+    <row r="632" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>308</v>
       </c>
@@ -22062,7 +22090,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="633" spans="1:10">
+    <row r="633" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>309</v>
       </c>
@@ -22094,7 +22122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="634" spans="1:10">
+    <row r="634" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>310</v>
       </c>
@@ -22126,7 +22154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:10">
+    <row r="635" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>311</v>
       </c>
@@ -22158,7 +22186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="636" spans="1:10">
+    <row r="636" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>312</v>
       </c>
@@ -22190,7 +22218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:10">
+    <row r="637" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>313</v>
       </c>
@@ -22222,7 +22250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="638" spans="1:10">
+    <row r="638" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>314</v>
       </c>
@@ -22254,7 +22282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="639" spans="1:10">
+    <row r="639" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>315</v>
       </c>
@@ -22286,7 +22314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="640" spans="1:10">
+    <row r="640" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>316</v>
       </c>
@@ -22318,7 +22346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="641" spans="1:10">
+    <row r="641" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>317</v>
       </c>
@@ -22350,7 +22378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="642" spans="1:10">
+    <row r="642" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>318</v>
       </c>
@@ -22382,7 +22410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="643" spans="1:10">
+    <row r="643" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>319</v>
       </c>
@@ -22414,7 +22442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="644" spans="1:10">
+    <row r="644" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>320</v>
       </c>
@@ -22446,7 +22474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="645" spans="1:10">
+    <row r="645" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>321</v>
       </c>
@@ -22478,7 +22506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:10">
+    <row r="646" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>322</v>
       </c>
@@ -22510,7 +22538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:10">
+    <row r="647" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>323</v>
       </c>
@@ -22542,7 +22570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:10">
+    <row r="648" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>324</v>
       </c>
@@ -22574,7 +22602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:10">
+    <row r="649" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>325</v>
       </c>
@@ -22606,7 +22634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="650" spans="1:10">
+    <row r="650" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>326</v>
       </c>
@@ -22638,7 +22666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:10">
+    <row r="651" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>327</v>
       </c>
@@ -22670,7 +22698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:10">
+    <row r="652" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>328</v>
       </c>
@@ -22702,7 +22730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653" spans="1:10">
+    <row r="653" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>329</v>
       </c>
@@ -22734,7 +22762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="654" spans="1:10">
+    <row r="654" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>330</v>
       </c>
@@ -22766,7 +22794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:10">
+    <row r="655" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>331</v>
       </c>
@@ -22798,7 +22826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="656" spans="1:10">
+    <row r="656" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>332</v>
       </c>
@@ -22830,7 +22858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:10">
+    <row r="657" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>333</v>
       </c>
@@ -22862,7 +22890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="658" spans="1:10">
+    <row r="658" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>334</v>
       </c>
@@ -22894,7 +22922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="659" spans="1:10">
+    <row r="659" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>335</v>
       </c>
@@ -22926,7 +22954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="660" spans="1:10">
+    <row r="660" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>336</v>
       </c>
@@ -22958,7 +22986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="661" spans="1:10">
+    <row r="661" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>337</v>
       </c>
@@ -22990,7 +23018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="662" spans="1:10">
+    <row r="662" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>338</v>
       </c>
@@ -23022,7 +23050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="663" spans="1:10">
+    <row r="663" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>339</v>
       </c>
@@ -23054,7 +23082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="664" spans="1:10">
+    <row r="664" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>340</v>
       </c>
@@ -23086,7 +23114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="665" spans="1:10">
+    <row r="665" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>341</v>
       </c>
@@ -23118,7 +23146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:10">
+    <row r="666" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>342</v>
       </c>
@@ -23150,7 +23178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="667" spans="1:10">
+    <row r="667" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>343</v>
       </c>
@@ -23182,7 +23210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:10">
+    <row r="668" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>344</v>
       </c>
@@ -23214,7 +23242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="669" spans="1:10">
+    <row r="669" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>345</v>
       </c>
@@ -23246,7 +23274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="670" spans="1:10">
+    <row r="670" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>296</v>
       </c>
@@ -23278,7 +23306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="671" spans="1:10">
+    <row r="671" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>297</v>
       </c>
@@ -23310,7 +23338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="672" spans="1:10">
+    <row r="672" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>298</v>
       </c>
@@ -23342,7 +23370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="673" spans="1:10">
+    <row r="673" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>299</v>
       </c>
@@ -23374,7 +23402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="674" spans="1:10">
+    <row r="674" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>300</v>
       </c>
@@ -23406,7 +23434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="675" spans="1:10">
+    <row r="675" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>301</v>
       </c>
@@ -23438,7 +23466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="676" spans="1:10">
+    <row r="676" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>302</v>
       </c>
@@ -23470,7 +23498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="677" spans="1:10">
+    <row r="677" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>303</v>
       </c>
@@ -23502,7 +23530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="678" spans="1:10">
+    <row r="678" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>304</v>
       </c>
@@ -23534,7 +23562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="679" spans="1:10">
+    <row r="679" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>305</v>
       </c>
@@ -23566,7 +23594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="680" spans="1:10">
+    <row r="680" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>306</v>
       </c>
@@ -23598,7 +23626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:10">
+    <row r="681" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>307</v>
       </c>
@@ -23630,7 +23658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="682" spans="1:10">
+    <row r="682" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>308</v>
       </c>
@@ -23662,7 +23690,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="683" spans="1:10">
+    <row r="683" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>309</v>
       </c>
@@ -23694,7 +23722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="684" spans="1:10">
+    <row r="684" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>310</v>
       </c>
@@ -23726,7 +23754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="685" spans="1:10">
+    <row r="685" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>311</v>
       </c>
@@ -23758,7 +23786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="686" spans="1:10">
+    <row r="686" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>312</v>
       </c>
@@ -23790,7 +23818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:10">
+    <row r="687" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>313</v>
       </c>
@@ -23822,7 +23850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="688" spans="1:10">
+    <row r="688" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>314</v>
       </c>
@@ -23854,7 +23882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="689" spans="1:10">
+    <row r="689" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>315</v>
       </c>
@@ -23886,7 +23914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690" spans="1:10">
+    <row r="690" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>316</v>
       </c>
@@ -23918,7 +23946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:10">
+    <row r="691" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>317</v>
       </c>
@@ -23950,7 +23978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="692" spans="1:10">
+    <row r="692" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>318</v>
       </c>
@@ -23982,7 +24010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="693" spans="1:10">
+    <row r="693" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>319</v>
       </c>
@@ -24014,7 +24042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="694" spans="1:10">
+    <row r="694" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>320</v>
       </c>
@@ -24046,7 +24074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="695" spans="1:10">
+    <row r="695" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>321</v>
       </c>
@@ -24078,7 +24106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="696" spans="1:10">
+    <row r="696" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>322</v>
       </c>
@@ -24110,7 +24138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="697" spans="1:10">
+    <row r="697" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>323</v>
       </c>
@@ -24142,7 +24170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:10">
+    <row r="698" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>324</v>
       </c>
@@ -24174,7 +24202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="699" spans="1:10">
+    <row r="699" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>325</v>
       </c>
@@ -24206,7 +24234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="700" spans="1:10">
+    <row r="700" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>326</v>
       </c>
@@ -24238,7 +24266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="701" spans="1:10">
+    <row r="701" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>327</v>
       </c>
@@ -24270,7 +24298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="702" spans="1:10">
+    <row r="702" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>328</v>
       </c>
@@ -24302,7 +24330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="703" spans="1:10">
+    <row r="703" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>329</v>
       </c>
@@ -24334,7 +24362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:10">
+    <row r="704" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>330</v>
       </c>
@@ -24366,7 +24394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="705" spans="1:10">
+    <row r="705" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>331</v>
       </c>
@@ -24398,7 +24426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="706" spans="1:10">
+    <row r="706" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>332</v>
       </c>
@@ -24430,7 +24458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="707" spans="1:10">
+    <row r="707" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>333</v>
       </c>
@@ -24462,7 +24490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="708" spans="1:10">
+    <row r="708" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>334</v>
       </c>
@@ -24494,7 +24522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="709" spans="1:10">
+    <row r="709" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>335</v>
       </c>
@@ -24526,7 +24554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="710" spans="1:10">
+    <row r="710" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>336</v>
       </c>
@@ -24558,7 +24586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="711" spans="1:10">
+    <row r="711" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>337</v>
       </c>
@@ -24590,7 +24618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="712" spans="1:10">
+    <row r="712" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>338</v>
       </c>
@@ -24622,7 +24650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:10">
+    <row r="713" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>339</v>
       </c>
@@ -24654,7 +24682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="714" spans="1:10">
+    <row r="714" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>340</v>
       </c>
@@ -24686,7 +24714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="715" spans="1:10">
+    <row r="715" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>341</v>
       </c>
@@ -24718,7 +24746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="716" spans="1:10">
+    <row r="716" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>342</v>
       </c>
@@ -24750,7 +24778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:10">
+    <row r="717" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>343</v>
       </c>
@@ -24782,7 +24810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:10">
+    <row r="718" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>344</v>
       </c>
@@ -24814,7 +24842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="719" spans="1:10">
+    <row r="719" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>345</v>
       </c>
@@ -24846,7 +24874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="720" spans="1:10">
+    <row r="720" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>346</v>
       </c>
@@ -24878,7 +24906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="721" spans="1:10">
+    <row r="721" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>347</v>
       </c>
@@ -24910,7 +24938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="722" spans="1:10">
+    <row r="722" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>348</v>
       </c>
@@ -24942,7 +24970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="723" spans="1:10">
+    <row r="723" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>349</v>
       </c>
@@ -24974,7 +25002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="724" spans="1:10">
+    <row r="724" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>350</v>
       </c>
@@ -25006,7 +25034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="725" spans="1:10">
+    <row r="725" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>351</v>
       </c>
@@ -25038,7 +25066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="726" spans="1:10">
+    <row r="726" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>352</v>
       </c>
@@ -25070,7 +25098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="727" spans="1:10">
+    <row r="727" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>353</v>
       </c>
@@ -25102,7 +25130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:10">
+    <row r="728" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>354</v>
       </c>
@@ -25134,7 +25162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:10">
+    <row r="729" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>355</v>
       </c>
@@ -25166,7 +25194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="730" spans="1:10">
+    <row r="730" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>356</v>
       </c>
@@ -25198,7 +25226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="731" spans="1:10">
+    <row r="731" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>357</v>
       </c>
@@ -25230,7 +25258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="732" spans="1:10">
+    <row r="732" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>358</v>
       </c>
@@ -25262,7 +25290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="733" spans="1:10">
+    <row r="733" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>359</v>
       </c>
@@ -25294,7 +25322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="734" spans="1:10">
+    <row r="734" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>360</v>
       </c>
@@ -25326,7 +25354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="735" spans="1:10">
+    <row r="735" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>361</v>
       </c>
@@ -25358,7 +25386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="736" spans="1:10">
+    <row r="736" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>362</v>
       </c>
@@ -25390,7 +25418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="737" spans="1:10">
+    <row r="737" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>363</v>
       </c>
@@ -25422,7 +25450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="738" spans="1:10">
+    <row r="738" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>357</v>
       </c>
@@ -25454,7 +25482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="739" spans="1:10">
+    <row r="739" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>364</v>
       </c>
@@ -25486,7 +25514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="740" spans="1:10">
+    <row r="740" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>365</v>
       </c>
@@ -25518,7 +25546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="741" spans="1:10">
+    <row r="741" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>366</v>
       </c>
@@ -25550,7 +25578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="742" spans="1:10">
+    <row r="742" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>367</v>
       </c>
@@ -25582,7 +25610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="743" spans="1:10">
+    <row r="743" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>368</v>
       </c>
@@ -25614,7 +25642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="744" spans="1:10">
+    <row r="744" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>369</v>
       </c>
@@ -25646,7 +25674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="745" spans="1:10">
+    <row r="745" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>370</v>
       </c>
@@ -25678,7 +25706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="1:10">
+    <row r="746" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>371</v>
       </c>
@@ -25710,7 +25738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="747" spans="1:10">
+    <row r="747" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>372</v>
       </c>
@@ -25742,7 +25770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="748" spans="1:10">
+    <row r="748" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>373</v>
       </c>
@@ -25774,7 +25802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="749" spans="1:10">
+    <row r="749" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>354</v>
       </c>
@@ -25806,7 +25834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="750" spans="1:10">
+    <row r="750" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>374</v>
       </c>
@@ -25838,7 +25866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:10">
+    <row r="751" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>375</v>
       </c>
@@ -25870,7 +25898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="752" spans="1:10">
+    <row r="752" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>376</v>
       </c>
@@ -25902,7 +25930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="753" spans="1:10">
+    <row r="753" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>377</v>
       </c>
@@ -25934,7 +25962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="754" spans="1:10">
+    <row r="754" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>378</v>
       </c>
@@ -25966,7 +25994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="755" spans="1:10">
+    <row r="755" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>354</v>
       </c>
@@ -25998,7 +26026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="1:10">
+    <row r="756" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>354</v>
       </c>
@@ -26030,7 +26058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="757" spans="1:10">
+    <row r="757" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>379</v>
       </c>
@@ -26062,7 +26090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="758" spans="1:10">
+    <row r="758" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>380</v>
       </c>
@@ -26094,7 +26122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="759" spans="1:10">
+    <row r="759" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>381</v>
       </c>
@@ -26126,7 +26154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="760" spans="1:10">
+    <row r="760" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>382</v>
       </c>
@@ -26158,7 +26186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="761" spans="1:10">
+    <row r="761" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>383</v>
       </c>
@@ -26190,7 +26218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="762" spans="1:10">
+    <row r="762" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>384</v>
       </c>
@@ -26222,7 +26250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="763" spans="1:10">
+    <row r="763" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>385</v>
       </c>
@@ -26254,7 +26282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="764" spans="1:10">
+    <row r="764" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>386</v>
       </c>
@@ -26286,7 +26314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="765" spans="1:10">
+    <row r="765" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>387</v>
       </c>
@@ -26318,7 +26346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="766" spans="1:10">
+    <row r="766" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>388</v>
       </c>
@@ -26350,7 +26378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="767" spans="1:10">
+    <row r="767" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>389</v>
       </c>
@@ -26382,7 +26410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="768" spans="1:10">
+    <row r="768" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>390</v>
       </c>
@@ -26414,7 +26442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="769" spans="1:10">
+    <row r="769" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>391</v>
       </c>
@@ -26446,7 +26474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="770" spans="1:10">
+    <row r="770" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>346</v>
       </c>
@@ -26478,7 +26506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="771" spans="1:10">
+    <row r="771" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>347</v>
       </c>
@@ -26510,7 +26538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="772" spans="1:10">
+    <row r="772" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>348</v>
       </c>
@@ -26542,7 +26570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="773" spans="1:10">
+    <row r="773" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>349</v>
       </c>
@@ -26574,7 +26602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="774" spans="1:10">
+    <row r="774" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>350</v>
       </c>
@@ -26606,7 +26634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="775" spans="1:10">
+    <row r="775" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>351</v>
       </c>
@@ -26638,7 +26666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="776" spans="1:10">
+    <row r="776" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>352</v>
       </c>
@@ -26670,7 +26698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="777" spans="1:10">
+    <row r="777" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>353</v>
       </c>
@@ -26702,7 +26730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="778" spans="1:10">
+    <row r="778" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>354</v>
       </c>
@@ -26734,7 +26762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="779" spans="1:10">
+    <row r="779" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>355</v>
       </c>
@@ -26766,7 +26794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="780" spans="1:10">
+    <row r="780" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>356</v>
       </c>
@@ -26798,7 +26826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="781" spans="1:10">
+    <row r="781" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>357</v>
       </c>
@@ -26830,7 +26858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="782" spans="1:10">
+    <row r="782" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>358</v>
       </c>
@@ -26862,7 +26890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="783" spans="1:10">
+    <row r="783" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>359</v>
       </c>
@@ -26894,7 +26922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="784" spans="1:10">
+    <row r="784" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>360</v>
       </c>
@@ -26926,7 +26954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="785" spans="1:10">
+    <row r="785" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>361</v>
       </c>
@@ -26958,7 +26986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="786" spans="1:10">
+    <row r="786" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>362</v>
       </c>
@@ -26990,7 +27018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="787" spans="1:10">
+    <row r="787" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>363</v>
       </c>
@@ -27022,7 +27050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="788" spans="1:10">
+    <row r="788" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>357</v>
       </c>
@@ -27054,7 +27082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="789" spans="1:10">
+    <row r="789" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>364</v>
       </c>
@@ -27086,7 +27114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="790" spans="1:10">
+    <row r="790" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>365</v>
       </c>
@@ -27118,7 +27146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="791" spans="1:10">
+    <row r="791" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>366</v>
       </c>
@@ -27150,7 +27178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="792" spans="1:10">
+    <row r="792" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>367</v>
       </c>
@@ -27182,7 +27210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="793" spans="1:10">
+    <row r="793" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>368</v>
       </c>
@@ -27214,7 +27242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="794" spans="1:10">
+    <row r="794" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>369</v>
       </c>
@@ -27246,7 +27274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="795" spans="1:10">
+    <row r="795" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>370</v>
       </c>
@@ -27278,7 +27306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="796" spans="1:10">
+    <row r="796" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>371</v>
       </c>
@@ -27310,7 +27338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="797" spans="1:10">
+    <row r="797" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>372</v>
       </c>
@@ -27342,7 +27370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="798" spans="1:10">
+    <row r="798" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>373</v>
       </c>
@@ -27374,7 +27402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="799" spans="1:10">
+    <row r="799" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>354</v>
       </c>
@@ -27406,7 +27434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="800" spans="1:10">
+    <row r="800" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>374</v>
       </c>
@@ -27438,7 +27466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="801" spans="1:10">
+    <row r="801" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>375</v>
       </c>
@@ -27470,7 +27498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="802" spans="1:10">
+    <row r="802" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>376</v>
       </c>
@@ -27502,7 +27530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="803" spans="1:10">
+    <row r="803" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>377</v>
       </c>
@@ -27534,7 +27562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="804" spans="1:10">
+    <row r="804" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>378</v>
       </c>
@@ -27566,7 +27594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="805" spans="1:10">
+    <row r="805" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>354</v>
       </c>
@@ -27598,7 +27626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="806" spans="1:10">
+    <row r="806" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>354</v>
       </c>
@@ -27630,7 +27658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="807" spans="1:10">
+    <row r="807" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>379</v>
       </c>
@@ -27662,7 +27690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="808" spans="1:10">
+    <row r="808" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>380</v>
       </c>
@@ -27694,7 +27722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="809" spans="1:10">
+    <row r="809" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>381</v>
       </c>
@@ -27726,7 +27754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="810" spans="1:10">
+    <row r="810" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>382</v>
       </c>
@@ -27758,7 +27786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="811" spans="1:10">
+    <row r="811" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>383</v>
       </c>
@@ -27790,7 +27818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="812" spans="1:10">
+    <row r="812" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>384</v>
       </c>
@@ -27822,7 +27850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="813" spans="1:10">
+    <row r="813" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>385</v>
       </c>
@@ -27854,7 +27882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="814" spans="1:10">
+    <row r="814" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>386</v>
       </c>
@@ -27886,7 +27914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="815" spans="1:10">
+    <row r="815" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>387</v>
       </c>
@@ -27918,7 +27946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="816" spans="1:10">
+    <row r="816" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>388</v>
       </c>
@@ -27950,7 +27978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="817" spans="1:10">
+    <row r="817" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>389</v>
       </c>
@@ -27982,7 +28010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="818" spans="1:10">
+    <row r="818" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>390</v>
       </c>
@@ -28014,7 +28042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="819" spans="1:10">
+    <row r="819" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>391</v>
       </c>
@@ -28046,7 +28074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="820" spans="1:10">
+    <row r="820" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>392</v>
       </c>
@@ -28078,7 +28106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="821" spans="1:10">
+    <row r="821" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>393</v>
       </c>
@@ -28110,7 +28138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="822" spans="1:10">
+    <row r="822" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>394</v>
       </c>
@@ -28142,7 +28170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="823" spans="1:10">
+    <row r="823" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>395</v>
       </c>
@@ -28174,7 +28202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="824" spans="1:10">
+    <row r="824" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>396</v>
       </c>
@@ -28206,7 +28234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="825" spans="1:10">
+    <row r="825" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>397</v>
       </c>
@@ -28238,7 +28266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="826" spans="1:10">
+    <row r="826" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>398</v>
       </c>
@@ -28270,7 +28298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="827" spans="1:10">
+    <row r="827" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>399</v>
       </c>
@@ -28302,7 +28330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="828" spans="1:10">
+    <row r="828" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>400</v>
       </c>
@@ -28334,7 +28362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="829" spans="1:10">
+    <row r="829" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>401</v>
       </c>
@@ -28366,7 +28394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="830" spans="1:10">
+    <row r="830" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>402</v>
       </c>
@@ -28398,7 +28426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="831" spans="1:10">
+    <row r="831" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>403</v>
       </c>
@@ -28430,7 +28458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="832" spans="1:10">
+    <row r="832" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>404</v>
       </c>
@@ -28462,7 +28490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="833" spans="1:10">
+    <row r="833" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>405</v>
       </c>
@@ -28494,7 +28522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="834" spans="1:10">
+    <row r="834" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>406</v>
       </c>
@@ -28526,7 +28554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="835" spans="1:10">
+    <row r="835" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>407</v>
       </c>
@@ -28558,7 +28586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="836" spans="1:10">
+    <row r="836" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>408</v>
       </c>
@@ -28590,7 +28618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="837" spans="1:10">
+    <row r="837" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>409</v>
       </c>
@@ -28622,7 +28650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="838" spans="1:10">
+    <row r="838" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>410</v>
       </c>
@@ -28654,7 +28682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="839" spans="1:10">
+    <row r="839" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>411</v>
       </c>
@@ -28686,7 +28714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="840" spans="1:10">
+    <row r="840" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>412</v>
       </c>
@@ -28718,7 +28746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="841" spans="1:10">
+    <row r="841" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>413</v>
       </c>
@@ -28750,7 +28778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="842" spans="1:10">
+    <row r="842" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>414</v>
       </c>
@@ -28782,7 +28810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="843" spans="1:10">
+    <row r="843" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>415</v>
       </c>
@@ -28814,7 +28842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="844" spans="1:10">
+    <row r="844" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>416</v>
       </c>
@@ -28846,7 +28874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="845" spans="1:10">
+    <row r="845" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>417</v>
       </c>
@@ -28878,7 +28906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="846" spans="1:10">
+    <row r="846" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>418</v>
       </c>
@@ -28910,7 +28938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="847" spans="1:10">
+    <row r="847" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>419</v>
       </c>
@@ -28942,7 +28970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="848" spans="1:10">
+    <row r="848" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>420</v>
       </c>
@@ -28974,7 +29002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="849" spans="1:10">
+    <row r="849" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>421</v>
       </c>
@@ -29006,7 +29034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="850" spans="1:10">
+    <row r="850" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>422</v>
       </c>
@@ -29038,7 +29066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="851" spans="1:10">
+    <row r="851" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>423</v>
       </c>
@@ -29070,7 +29098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="852" spans="1:10">
+    <row r="852" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>424</v>
       </c>
@@ -29102,7 +29130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="853" spans="1:10">
+    <row r="853" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>425</v>
       </c>
@@ -29134,7 +29162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="854" spans="1:10">
+    <row r="854" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>426</v>
       </c>
@@ -29166,7 +29194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="855" spans="1:10">
+    <row r="855" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>427</v>
       </c>
@@ -29198,7 +29226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="856" spans="1:10">
+    <row r="856" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>428</v>
       </c>
@@ -29230,7 +29258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="857" spans="1:10">
+    <row r="857" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>429</v>
       </c>
@@ -29262,7 +29290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="858" spans="1:10">
+    <row r="858" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>430</v>
       </c>
@@ -29294,7 +29322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="859" spans="1:10">
+    <row r="859" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>431</v>
       </c>
@@ -29326,7 +29354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="860" spans="1:10">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>432</v>
       </c>
@@ -29358,7 +29386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="861" spans="1:10">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>433</v>
       </c>
@@ -29390,7 +29418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="862" spans="1:10">
+    <row r="862" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>434</v>
       </c>
@@ -29422,7 +29450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="863" spans="1:10">
+    <row r="863" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>435</v>
       </c>
@@ -29454,7 +29482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="864" spans="1:10">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>436</v>
       </c>
@@ -29486,7 +29514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="865" spans="1:10">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>437</v>
       </c>
@@ -29518,7 +29546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="866" spans="1:10">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>438</v>
       </c>
@@ -29550,7 +29578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="867" spans="1:10">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>439</v>
       </c>
@@ -29582,7 +29610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="868" spans="1:10">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>440</v>
       </c>
@@ -29614,7 +29642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="869" spans="1:10">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>441</v>
       </c>
@@ -29646,7 +29674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="870" spans="1:10">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>392</v>
       </c>
@@ -29678,7 +29706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="871" spans="1:10">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>393</v>
       </c>
@@ -29710,7 +29738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="872" spans="1:10">
+    <row r="872" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>394</v>
       </c>
@@ -29742,7 +29770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="873" spans="1:10">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>395</v>
       </c>
@@ -29774,7 +29802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="874" spans="1:10">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>396</v>
       </c>
@@ -29806,7 +29834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="875" spans="1:10">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>397</v>
       </c>
@@ -29838,7 +29866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="876" spans="1:10">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>398</v>
       </c>
@@ -29870,7 +29898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="877" spans="1:10">
+    <row r="877" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>399</v>
       </c>
@@ -29902,7 +29930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="878" spans="1:10">
+    <row r="878" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>400</v>
       </c>
@@ -29934,7 +29962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="879" spans="1:10">
+    <row r="879" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>401</v>
       </c>
@@ -29966,7 +29994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="880" spans="1:10">
+    <row r="880" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>402</v>
       </c>
@@ -29998,7 +30026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="881" spans="1:10">
+    <row r="881" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>403</v>
       </c>
@@ -30030,7 +30058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="882" spans="1:10">
+    <row r="882" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>404</v>
       </c>
@@ -30062,7 +30090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="883" spans="1:10">
+    <row r="883" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>405</v>
       </c>
@@ -30094,7 +30122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="884" spans="1:10">
+    <row r="884" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>406</v>
       </c>
@@ -30126,7 +30154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="885" spans="1:10">
+    <row r="885" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>407</v>
       </c>
@@ -30158,7 +30186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="886" spans="1:10">
+    <row r="886" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>408</v>
       </c>
@@ -30190,7 +30218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="887" spans="1:10">
+    <row r="887" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>409</v>
       </c>
@@ -30222,7 +30250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="888" spans="1:10">
+    <row r="888" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>410</v>
       </c>
@@ -30254,7 +30282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="889" spans="1:10">
+    <row r="889" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>411</v>
       </c>
@@ -30286,7 +30314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="890" spans="1:10">
+    <row r="890" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>412</v>
       </c>
@@ -30318,7 +30346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="891" spans="1:10">
+    <row r="891" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>413</v>
       </c>
@@ -30350,7 +30378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="892" spans="1:10">
+    <row r="892" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>414</v>
       </c>
@@ -30382,7 +30410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="893" spans="1:10">
+    <row r="893" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>415</v>
       </c>
@@ -30414,7 +30442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="894" spans="1:10">
+    <row r="894" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>416</v>
       </c>
@@ -30446,7 +30474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="895" spans="1:10">
+    <row r="895" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>417</v>
       </c>
@@ -30478,7 +30506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="896" spans="1:10">
+    <row r="896" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>418</v>
       </c>
@@ -30510,7 +30538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="897" spans="1:10">
+    <row r="897" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>419</v>
       </c>
@@ -30542,7 +30570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="898" spans="1:10">
+    <row r="898" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>420</v>
       </c>
@@ -30574,7 +30602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="899" spans="1:10">
+    <row r="899" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>421</v>
       </c>
@@ -30606,7 +30634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="900" spans="1:10">
+    <row r="900" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>422</v>
       </c>
@@ -30638,7 +30666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="901" spans="1:10">
+    <row r="901" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>423</v>
       </c>
@@ -30670,7 +30698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="902" spans="1:10">
+    <row r="902" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>424</v>
       </c>
@@ -30702,7 +30730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="903" spans="1:10">
+    <row r="903" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>425</v>
       </c>
@@ -30734,7 +30762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="904" spans="1:10">
+    <row r="904" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>426</v>
       </c>
@@ -30766,7 +30794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="905" spans="1:10">
+    <row r="905" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>427</v>
       </c>
@@ -30798,7 +30826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="906" spans="1:10">
+    <row r="906" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>428</v>
       </c>
@@ -30830,7 +30858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="907" spans="1:10">
+    <row r="907" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>429</v>
       </c>
@@ -30862,7 +30890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="908" spans="1:10">
+    <row r="908" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>430</v>
       </c>
@@ -30894,7 +30922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="909" spans="1:10">
+    <row r="909" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>431</v>
       </c>
@@ -30926,7 +30954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="910" spans="1:10">
+    <row r="910" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>432</v>
       </c>
@@ -30958,7 +30986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="911" spans="1:10">
+    <row r="911" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>433</v>
       </c>
@@ -30990,7 +31018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="912" spans="1:10">
+    <row r="912" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>434</v>
       </c>
@@ -31022,7 +31050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="913" spans="1:10">
+    <row r="913" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>435</v>
       </c>
@@ -31054,7 +31082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="914" spans="1:10">
+    <row r="914" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>436</v>
       </c>
@@ -31086,7 +31114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="915" spans="1:10">
+    <row r="915" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>437</v>
       </c>
@@ -31118,7 +31146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="916" spans="1:10">
+    <row r="916" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>438</v>
       </c>
@@ -31150,7 +31178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="917" spans="1:10">
+    <row r="917" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>439</v>
       </c>
@@ -31182,7 +31210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="918" spans="1:10">
+    <row r="918" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>440</v>
       </c>
@@ -31214,7 +31242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="919" spans="1:10">
+    <row r="919" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>441</v>
       </c>
@@ -31246,7 +31274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="920" spans="1:10">
+    <row r="920" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>442</v>
       </c>
@@ -31278,7 +31306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="921" spans="1:10">
+    <row r="921" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>443</v>
       </c>
@@ -31310,7 +31338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="922" spans="1:10">
+    <row r="922" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>444</v>
       </c>
@@ -31342,7 +31370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="923" spans="1:10">
+    <row r="923" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>445</v>
       </c>
@@ -31374,7 +31402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="924" spans="1:10">
+    <row r="924" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>446</v>
       </c>
@@ -31406,7 +31434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="925" spans="1:10">
+    <row r="925" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>447</v>
       </c>
@@ -31438,7 +31466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="926" spans="1:10">
+    <row r="926" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>448</v>
       </c>
@@ -31470,7 +31498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="927" spans="1:10">
+    <row r="927" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>449</v>
       </c>
@@ -31502,7 +31530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="928" spans="1:10">
+    <row r="928" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>450</v>
       </c>
@@ -31534,7 +31562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="929" spans="1:10">
+    <row r="929" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>451</v>
       </c>
@@ -31566,7 +31594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="930" spans="1:10">
+    <row r="930" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>452</v>
       </c>
@@ -31598,7 +31626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="931" spans="1:10">
+    <row r="931" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>453</v>
       </c>
@@ -31630,7 +31658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="932" spans="1:10">
+    <row r="932" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>454</v>
       </c>
@@ -31662,7 +31690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="933" spans="1:10">
+    <row r="933" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>455</v>
       </c>
@@ -31694,7 +31722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="934" spans="1:10">
+    <row r="934" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>456</v>
       </c>
@@ -31726,7 +31754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="935" spans="1:10">
+    <row r="935" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>457</v>
       </c>
@@ -31758,7 +31786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="936" spans="1:10">
+    <row r="936" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>458</v>
       </c>
@@ -31790,7 +31818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="937" spans="1:10">
+    <row r="937" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>459</v>
       </c>
@@ -31822,7 +31850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="938" spans="1:10">
+    <row r="938" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
         <v>460</v>
       </c>
@@ -31854,7 +31882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="939" spans="1:10">
+    <row r="939" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>460</v>
       </c>
@@ -31886,7 +31914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="940" spans="1:10">
+    <row r="940" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>461</v>
       </c>
@@ -31918,7 +31946,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="941" spans="1:10">
+    <row r="941" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>462</v>
       </c>
@@ -31950,7 +31978,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="942" spans="1:10">
+    <row r="942" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>462</v>
       </c>
@@ -31982,7 +32010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="943" spans="1:10">
+    <row r="943" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>463</v>
       </c>
@@ -32014,7 +32042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="944" spans="1:10">
+    <row r="944" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
         <v>464</v>
       </c>
@@ -32046,7 +32074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="945" spans="1:10">
+    <row r="945" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
         <v>465</v>
       </c>
@@ -32078,7 +32106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="946" spans="1:10">
+    <row r="946" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>466</v>
       </c>
@@ -32110,7 +32138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="947" spans="1:10">
+    <row r="947" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
         <v>467</v>
       </c>
@@ -32142,7 +32170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="948" spans="1:10">
+    <row r="948" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
         <v>468</v>
       </c>
@@ -32174,7 +32202,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="949" spans="1:10">
+    <row r="949" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
         <v>469</v>
       </c>
@@ -32206,7 +32234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="950" spans="1:10">
+    <row r="950" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>470</v>
       </c>
@@ -32238,7 +32266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="951" spans="1:10">
+    <row r="951" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
         <v>471</v>
       </c>
@@ -32270,7 +32298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="952" spans="1:10">
+    <row r="952" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>472</v>
       </c>
@@ -32302,7 +32330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="953" spans="1:10">
+    <row r="953" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>473</v>
       </c>
@@ -32334,7 +32362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="954" spans="1:10">
+    <row r="954" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>474</v>
       </c>
@@ -32366,7 +32394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="955" spans="1:10">
+    <row r="955" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>12</v>
       </c>
@@ -32398,7 +32426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="956" spans="1:10">
+    <row r="956" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>475</v>
       </c>
@@ -32430,7 +32458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="957" spans="1:10">
+    <row r="957" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>476</v>
       </c>
@@ -32462,7 +32490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="958" spans="1:10">
+    <row r="958" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>477</v>
       </c>
@@ -32494,7 +32522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="959" spans="1:10">
+    <row r="959" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>478</v>
       </c>
@@ -32526,7 +32554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="960" spans="1:10">
+    <row r="960" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>479</v>
       </c>
@@ -32558,7 +32586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="961" spans="1:10">
+    <row r="961" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>12</v>
       </c>
@@ -32590,7 +32618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="962" spans="1:10">
+    <row r="962" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>480</v>
       </c>
@@ -32622,7 +32650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="963" spans="1:10">
+    <row r="963" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>481</v>
       </c>
@@ -32654,7 +32682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="964" spans="1:10">
+    <row r="964" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>482</v>
       </c>
@@ -32686,7 +32714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="965" spans="1:10">
+    <row r="965" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>483</v>
       </c>
@@ -32718,7 +32746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="966" spans="1:10">
+    <row r="966" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>484</v>
       </c>
@@ -32750,7 +32778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="967" spans="1:10">
+    <row r="967" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
         <v>485</v>
       </c>
@@ -32782,7 +32810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="968" spans="1:10">
+    <row r="968" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>486</v>
       </c>
@@ -32814,7 +32842,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="969" spans="1:10">
+    <row r="969" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>442</v>
       </c>
@@ -32846,7 +32874,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="970" spans="1:10">
+    <row r="970" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>443</v>
       </c>
@@ -32878,7 +32906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="971" spans="1:10">
+    <row r="971" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>444</v>
       </c>
@@ -32910,7 +32938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="972" spans="1:10">
+    <row r="972" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>445</v>
       </c>
@@ -32942,7 +32970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="973" spans="1:10">
+    <row r="973" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>446</v>
       </c>
@@ -32974,7 +33002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="974" spans="1:10">
+    <row r="974" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>447</v>
       </c>
@@ -33006,7 +33034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="975" spans="1:10">
+    <row r="975" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>448</v>
       </c>
@@ -33038,7 +33066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="976" spans="1:10">
+    <row r="976" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>449</v>
       </c>
@@ -33070,7 +33098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="977" spans="1:10">
+    <row r="977" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>450</v>
       </c>
@@ -33102,7 +33130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="978" spans="1:10">
+    <row r="978" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>451</v>
       </c>
@@ -33134,7 +33162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="979" spans="1:10">
+    <row r="979" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>452</v>
       </c>
@@ -33166,7 +33194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="980" spans="1:10">
+    <row r="980" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>453</v>
       </c>
@@ -33198,7 +33226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="981" spans="1:10">
+    <row r="981" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>454</v>
       </c>
@@ -33230,7 +33258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="982" spans="1:10">
+    <row r="982" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>455</v>
       </c>
@@ -33262,7 +33290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="983" spans="1:10">
+    <row r="983" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>456</v>
       </c>
@@ -33294,7 +33322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="984" spans="1:10">
+    <row r="984" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>457</v>
       </c>
@@ -33326,7 +33354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="985" spans="1:10">
+    <row r="985" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>458</v>
       </c>
@@ -33358,7 +33386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="986" spans="1:10">
+    <row r="986" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>459</v>
       </c>
@@ -33390,7 +33418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="987" spans="1:10">
+    <row r="987" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>460</v>
       </c>
@@ -33422,7 +33450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="988" spans="1:10">
+    <row r="988" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>460</v>
       </c>
@@ -33454,7 +33482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="989" spans="1:10">
+    <row r="989" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>461</v>
       </c>
@@ -33486,7 +33514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="990" spans="1:10">
+    <row r="990" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>462</v>
       </c>
@@ -33518,7 +33546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="991" spans="1:10">
+    <row r="991" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>462</v>
       </c>
@@ -33550,7 +33578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="992" spans="1:10">
+    <row r="992" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>463</v>
       </c>
@@ -33582,7 +33610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="993" spans="1:10">
+    <row r="993" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
         <v>464</v>
       </c>
@@ -33614,7 +33642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="994" spans="1:10">
+    <row r="994" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
         <v>465</v>
       </c>
@@ -33646,7 +33674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="995" spans="1:10">
+    <row r="995" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
         <v>466</v>
       </c>
@@ -33678,7 +33706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="996" spans="1:10">
+    <row r="996" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
         <v>467</v>
       </c>
@@ -33710,7 +33738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="997" spans="1:10">
+    <row r="997" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
         <v>468</v>
       </c>
@@ -33742,7 +33770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="998" spans="1:10">
+    <row r="998" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
         <v>469</v>
       </c>
@@ -33774,7 +33802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="999" spans="1:10">
+    <row r="999" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
         <v>470</v>
       </c>
@@ -33806,7 +33834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1000" spans="1:10">
+    <row r="1000" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
         <v>471</v>
       </c>
@@ -33838,7 +33866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1001" spans="1:10">
+    <row r="1001" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
         <v>472</v>
       </c>
@@ -33870,7 +33898,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1002" spans="1:10">
+    <row r="1002" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
         <v>473</v>
       </c>
@@ -33902,7 +33930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1003" spans="1:10">
+    <row r="1003" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
         <v>474</v>
       </c>
@@ -33934,7 +33962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1004" spans="1:10">
+    <row r="1004" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1004" t="s">
         <v>12</v>
       </c>
@@ -33966,7 +33994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1005" spans="1:10">
+    <row r="1005" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
         <v>475</v>
       </c>
@@ -33998,7 +34026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1006" spans="1:10">
+    <row r="1006" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
         <v>476</v>
       </c>
@@ -34030,7 +34058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1007" spans="1:10">
+    <row r="1007" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
         <v>477</v>
       </c>
@@ -34062,7 +34090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1008" spans="1:10">
+    <row r="1008" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
         <v>478</v>
       </c>
@@ -34094,7 +34122,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1009" spans="1:10">
+    <row r="1009" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
         <v>479</v>
       </c>
@@ -34126,7 +34154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1010" spans="1:10">
+    <row r="1010" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
         <v>12</v>
       </c>
@@ -34158,7 +34186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1011" spans="1:10">
+    <row r="1011" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
         <v>480</v>
       </c>
@@ -34190,7 +34218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1012" spans="1:10">
+    <row r="1012" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
         <v>481</v>
       </c>
@@ -34222,7 +34250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1013" spans="1:10">
+    <row r="1013" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
         <v>482</v>
       </c>
@@ -34254,7 +34282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1014" spans="1:10">
+    <row r="1014" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1014" t="s">
         <v>483</v>
       </c>
@@ -34286,7 +34314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1015" spans="1:10">
+    <row r="1015" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
         <v>484</v>
       </c>
@@ -34318,7 +34346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1016" spans="1:10">
+    <row r="1016" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
         <v>485</v>
       </c>
@@ -34350,7 +34378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1017" spans="1:10">
+    <row r="1017" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
         <v>486</v>
       </c>
